--- a/02_加值成品/九上/九上5-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上5-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上5-2 組成地殼的物質　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上5-2 組成地殼的物質　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>岩石由什麼組成？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>層理</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>火成岩</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>礦物</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>組成</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>地殼主要由什麼構成？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>層理</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>變質岩</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>岩石</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>岩層</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>岩漿冷卻凝固形成？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>火成岩</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>變質岩</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>礦物</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>冷凝</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>碎屑沉積膠結形成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>大理岩</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>沉積岩</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>石灰岩</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>無機固體</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>堆積</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>受高溫高壓變質形成？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>變質岩</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>岩石</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>石灰岩</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>變質</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>化石主要見於哪類岩石？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>岩石</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>沉積岩</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>變質岩</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>大理岩</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>層理</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>花岡岩屬哪類岩石？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>大理岩</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>礦物</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>火成岩</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>火成沉積變質</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>冷凝</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>大理岩屬哪類岩石？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>變質岩</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>石灰岩</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>層理</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>礦物</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>石灰岩變質</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>組成岩石的天然無機固體是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>火成岩</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>岩石</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>礦物</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>礦物</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>依成因岩石分成哪三大類？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>火成沉積變質</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>礦物</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>大理岩</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>三類</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上5-2 組成地殼的物質　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上5-2 組成地殼的物質　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>玄武岩屬哪類岩石？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>火成岩</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>岩石</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>石灰岩</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>岩漿</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>砂岩頁岩屬哪類？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>層理</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>火成沉積變質</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>岩石</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>沉積岩</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>沉積</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>沉積岩常見的構造？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>層理</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>石灰岩</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>礦物</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>分層</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>石灰岩受變質變成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>大理岩</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>石灰岩</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>礦物</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>變質</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>礦物是天然的什麼固體？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>火成岩</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>無機固體</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>礦物</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>天然</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>岩漿在地下慢冷結晶較？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>礦物</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>慢冷</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>沉積岩為何常含化石？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>火成沉積變質可經風化沉積或高溫高壓互轉</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>慢冷結晶大、快冷結晶小</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>沉積環境與年代</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>生物遺骸隨沉積埋藏</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>保存</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>岩漿噴出地表快冷結晶？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>小</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>礦物組成岩石</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>火成岩</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>變質岩</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>快冷</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>石灰岩經高溫高壓變成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>大理岩</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>火成岩</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>層理</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>火成沉積變質</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>變質</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>含有層理的岩石多為？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>變質岩</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>礦物</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>石灰岩</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>沉積岩</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>層理</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上5-2 組成地殼的物質　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上5-2 組成地殼的物質　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>三大類岩石如何互相轉變(岩石循環)？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>火成沉積變質可經風化沉積或高溫高壓互轉</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>成分與冷卻環境(深成/噴出)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>將岩石破碎成沉積物</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>受高溫高壓變質</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>循環</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何沉積岩最可能找到化石？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>慢冷結晶大、快冷結晶小</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>沉積環境與年代</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>將岩石破碎成沉積物</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>低溫堆積可保存生物遺骸</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>成因</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>冷卻快慢如何影響火成岩結晶大小？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>慢冷結晶大、快冷結晶小</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>沉積環境與年代</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>成分與冷卻環境(深成/噴出)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>將岩石破碎成沉積物</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>結晶</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>由層理與化石可推知岩石？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>沉積環境與年代</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>慢冷結晶大、快冷結晶小</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>受高溫高壓變質</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>將岩石破碎成沉積物</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>推論</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>大理岩由何岩石變質而來？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>石灰岩</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>礦物</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>火成岩</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>變質</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>岩石與礦物的層級關係？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>石灰岩</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>礦物</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>礦物組成岩石</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>層級</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>風化侵蝕在岩石循環的角色？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>慢冷結晶大、快冷結晶小</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>生物遺骸隨沉積埋藏</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>將岩石破碎成沉積物</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>沉積環境與年代</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>過程</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>花岡岩與玄武岩同為火成岩差別在？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>慢冷結晶大、快冷結晶小</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>生物遺骸隨沉積埋藏</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>低溫堆積可保存生物遺骸</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>成分與冷卻環境(深成/噴出)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>細分</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>岩石循環中沉積岩如何變成變質岩？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>受高溫高壓變質</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>成分與冷卻環境(深成/噴出)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>沉積環境與年代</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>火成沉積變質可經風化沉積或高溫高壓互轉</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>循環</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>由岩石含化石可初步判斷屬？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>層理</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>大理岩</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>沉積岩</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>判別</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上5-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上5-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>組成</t>
+          <t>組成：岩石是由一種或多種礦物顆粒結合在一起所構成的</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>岩層</t>
+          <t>岩層：地球最外層的地殼,主要就是由各種岩石堆疊組成的</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>冷凝</t>
+          <t>冷凝：地底炙熱的岩漿溫度下降後凝固變硬,就形成了火成岩</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>堆積</t>
+          <t>堆積：岩石碎屑一層層堆積,再被礦物質黏結固化,就形成沉積岩</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>變質</t>
+          <t>變質：原本的岩石在地底受到很高的溫度和壓力,結構改變後形成變質岩</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>層理</t>
+          <t>層理：生物遺骸容易隨著沉積物一層層被掩埋保存,所以化石多在沉積岩裡</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>冷凝</t>
+          <t>冷凝：花岡岩是岩漿在地底慢慢冷卻凝固後形成的,屬於火成岩</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>石灰岩變質</t>
+          <t>石灰岩變質：大理岩是由石灰岩經過高溫高壓變質作用形成的</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>礦物</t>
+          <t>礦物：礦物是自然界中天然形成的無機固體,一種或多種礦物聚集在一起就構成了岩石</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>三類</t>
+          <t>三類：依照形成的原因,岩石可分為火成岩(岩漿冷卻)、沉積岩(碎屑堆積)、變質岩(高溫高壓變質)三大類</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>岩漿</t>
+          <t>岩漿：玄武岩是岩漿噴出地表快速冷卻凝固形成的,屬於火成岩</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>沉積</t>
+          <t>沉積：砂岩和頁岩都是由碎屑物質一層層沉積堆積膠結而成的</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>分層</t>
+          <t>分層：沉積岩因為是一層層堆積形成的,常常可以看到清楚的分層構造</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>變質</t>
+          <t>變質：石灰岩在高溫高壓的環境下,結構重新排列變成了大理岩</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>天然</t>
+          <t>天然：礦物是自然界中天然形成、非生物體的固體物質</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>慢冷</t>
+          <t>慢冷：岩漿在地底冷卻速度慢,有充分時間讓礦物結晶長得比較大顆</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>保存</t>
+          <t>保存：生物死亡後遺骸容易被沉積物慢慢覆蓋掩埋,長期保存下來變成化石</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>快冷</t>
+          <t>快冷：岩漿噴出地表接觸空氣冷卻得很快,礦物來不及長大結晶就變小顆</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>變質</t>
+          <t>變質：石灰岩若受到地底的高溫與高壓作用,礦物結構會重新排列,變質形成大理岩</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>層理</t>
+          <t>層理：沉積岩是碎屑物一層層堆積膠結而成,常保留清楚的層狀構造,稱為層理</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>循環</t>
+          <t>循環：火成岩經風化侵蝕變成沉積物再形成沉積岩,岩石受高溫高壓能變質,三者能在地球內外力作用下不斷互相轉變</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>成因</t>
+          <t>成因：沉積岩形成過程溫度低、是慢慢一層層堆積掩埋,能完整保存生物遺骸的形狀</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>結晶</t>
+          <t>結晶：冷卻越慢,礦物有越多時間慢慢長大,結晶顆粒就越大;冷卻越快結晶就越細小</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>推論</t>
+          <t>推論：從岩層排列的層理和裡面的化石種類,可以推測這塊岩石當初形成的環境和大約年代</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>變質</t>
+          <t>變質：大理岩是石灰岩經過地底高溫高壓的變質作用轉變而成的</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>層級</t>
+          <t>層級：礦物是比較基本的物質單位,許多礦物顆粒結合在一起就構成了岩石</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>過程</t>
+          <t>過程：風化和侵蝕會把大塊岩石慢慢打碎成小碎屑,成為之後形成沉積岩的原料</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>細分</t>
+          <t>細分：花岡岩是岩漿在地底深處慢慢冷卻形成,玄武岩則是岩漿噴出地表快速冷卻形成,兩者成分和冷卻環境不同</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>循環</t>
+          <t>循環：沉積岩若被深埋到地底,受到很高的溫度和壓力作用,結構改變後就會變質成變質岩,這是岩石循環的一環</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>判別</t>
+          <t>判別：化石主要是生物遺骸被沉積物掩埋保存下來的,所以只要岩石中含有化石,通常可以判斷它是沉積岩</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上5-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上5-2_三種難度測驗卷.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>層理</t>
+          <t>火成沉積變質</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>火成岩</t>
+          <t>變質岩</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>大</t>
+          <t>大理岩</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -603,17 +603,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>層理</t>
+          <t>大</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>變質岩</t>
+          <t>石灰岩</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>小</t>
+          <t>火成沉積變質</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -883,17 +883,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>小</t>
+          <t>沉積岩</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>火成岩</t>
+          <t>岩石</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>岩石</t>
+          <t>火成沉積變質</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>石灰岩</t>
+          <t>沉積岩</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>礦物</t>
+          <t>岩石</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>沉積岩</t>
+          <t>火成沉積變質</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1239,17 +1239,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>沉積岩</t>
+          <t>礦物</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>小</t>
+          <t>石灰岩</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>礦物</t>
+          <t>層理</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>火成岩</t>
+          <t>小</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>層理</t>
+          <t>岩石</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>火成沉積變質</t>
+          <t>變質岩</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>火成沉積變質</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
           <t>小</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>石灰岩</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>礦物</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
